--- a/4. Unregistered_Manual_Map.xlsx
+++ b/4. Unregistered_Manual_Map.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wylie\Downloads\Python Environment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BF93CE1-4DFB-4ACE-ACC7-7C9D2EB62EE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5258288D-A0B9-4886-9D3B-5D55F258ECDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19920" yWindow="600" windowWidth="18270" windowHeight="20250" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="29475" windowHeight="18645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,190 +28,190 @@
     <t>Team</t>
   </si>
   <si>
+    <t>CI</t>
+  </si>
+  <si>
+    <t>Ali Quadri</t>
+  </si>
+  <si>
+    <t>Cooke Collegians</t>
+  </si>
+  <si>
+    <t>Alisha McKee</t>
+  </si>
+  <si>
+    <t>Archie McDowell</t>
+  </si>
+  <si>
+    <t>CSNI</t>
+  </si>
+  <si>
+    <t>Ava Templeton</t>
+  </si>
+  <si>
+    <t>Lisburn</t>
+  </si>
+  <si>
+    <t>Ayla Boyd</t>
+  </si>
+  <si>
+    <t>Dundrum</t>
+  </si>
+  <si>
+    <t>Bradley Hodge</t>
+  </si>
+  <si>
+    <t>Muckamore</t>
+  </si>
+  <si>
+    <t>Christy Rathesh</t>
+  </si>
+  <si>
+    <t>Cora Perrin</t>
+  </si>
+  <si>
+    <t>Danny Moby</t>
+  </si>
+  <si>
+    <t>Victoria</t>
+  </si>
+  <si>
+    <t>Dave Williams</t>
+  </si>
+  <si>
+    <t>Edward Lawther</t>
+  </si>
+  <si>
+    <t>Ellie Hipson</t>
+  </si>
+  <si>
+    <t>Erin Smyth</t>
+  </si>
+  <si>
+    <t>Harry Knox</t>
+  </si>
+  <si>
+    <t>Cliftonville Academy</t>
+  </si>
+  <si>
+    <t>Indie Allen</t>
+  </si>
+  <si>
+    <t>Isla McMullan</t>
+  </si>
+  <si>
+    <t>Jack Mayne</t>
+  </si>
+  <si>
+    <t>Jacob Lawther</t>
+  </si>
+  <si>
+    <t>James Cockcroft</t>
+  </si>
+  <si>
+    <t>Donacloney Mill</t>
+  </si>
+  <si>
+    <t>James Montgomery</t>
+  </si>
+  <si>
+    <t>James Wootton</t>
+  </si>
+  <si>
+    <t>Instonians</t>
+  </si>
+  <si>
+    <t>Joel McKean</t>
+  </si>
+  <si>
+    <t>Josh Hall</t>
+  </si>
+  <si>
+    <t>Karin Gul</t>
+  </si>
+  <si>
+    <t>Katie Harper</t>
+  </si>
+  <si>
+    <t>Lea Matthews</t>
+  </si>
+  <si>
+    <t>Templepatrick</t>
+  </si>
+  <si>
+    <t>Lyla Cubitt</t>
+  </si>
+  <si>
+    <t>Manjit Singh</t>
+  </si>
+  <si>
+    <t>PSNI</t>
+  </si>
+  <si>
+    <t>Maurya Shukla</t>
+  </si>
+  <si>
+    <t>Molly Sawyer</t>
+  </si>
+  <si>
+    <t>Oliver Bryans</t>
+  </si>
+  <si>
+    <t>Olivia Boyd</t>
+  </si>
+  <si>
+    <t>Rachel Murray</t>
+  </si>
+  <si>
+    <t>Rowan Foye</t>
+  </si>
+  <si>
+    <t>Bangor</t>
+  </si>
+  <si>
+    <t>Sarah Cowden</t>
+  </si>
+  <si>
+    <t>Shanmukh Kasibhatla</t>
+  </si>
+  <si>
+    <t>Tom Livingston</t>
+  </si>
+  <si>
     <t>Tyler McGladdery</t>
   </si>
   <si>
-    <t>Aidan O'Gorman</t>
-  </si>
-  <si>
-    <t>Edward Lawther</t>
-  </si>
-  <si>
-    <t>Jacob Lawther</t>
-  </si>
-  <si>
-    <t>James Cockcroft</t>
-  </si>
-  <si>
-    <t>Karin Gul</t>
-  </si>
-  <si>
-    <t>Oliver Bryans</t>
-  </si>
-  <si>
     <t>Derriaghy</t>
   </si>
   <si>
-    <t>CI</t>
+    <t>Usman Ahmed</t>
+  </si>
+  <si>
+    <t>Usman Siddiq</t>
+  </si>
+  <si>
+    <t>Vismithaa Pandiaraj</t>
+  </si>
+  <si>
+    <t>Aidan O'Gormon</t>
+  </si>
+  <si>
+    <t>NCU Pathway XI</t>
+  </si>
+  <si>
+    <t>Drumaness Superkings</t>
+  </si>
+  <si>
+    <t>Holywood 1881</t>
+  </si>
+  <si>
+    <t>Ards &amp; Donaghadee</t>
+  </si>
+  <si>
+    <t>Ballymena</t>
   </si>
   <si>
     <t>Belfast</t>
-  </si>
-  <si>
-    <t>Ards &amp; Donaghadee</t>
-  </si>
-  <si>
-    <t>Donacloney Mill</t>
-  </si>
-  <si>
-    <t>Victoria</t>
-  </si>
-  <si>
-    <t>Bradley Hodge</t>
-  </si>
-  <si>
-    <t>Shanmukh Kasibhatla</t>
-  </si>
-  <si>
-    <t>Maurya Shukla</t>
-  </si>
-  <si>
-    <t>Harry Knox</t>
-  </si>
-  <si>
-    <t>Tom Livingston</t>
-  </si>
-  <si>
-    <t>James Wootton</t>
-  </si>
-  <si>
-    <t>Archie McDowell</t>
-  </si>
-  <si>
-    <t>Alisha McKee</t>
-  </si>
-  <si>
-    <t>Isla McMullan</t>
-  </si>
-  <si>
-    <t>Ayla Boyd</t>
-  </si>
-  <si>
-    <t>Jack Mayne</t>
-  </si>
-  <si>
-    <t>Manjit Singh</t>
-  </si>
-  <si>
-    <t>Muckamore</t>
-  </si>
-  <si>
-    <t>Instonians</t>
-  </si>
-  <si>
-    <t>Cooke Collegians</t>
-  </si>
-  <si>
-    <t>Cliftonville Academy</t>
-  </si>
-  <si>
-    <t>CSNI</t>
-  </si>
-  <si>
-    <t>Drumaness Superkings</t>
-  </si>
-  <si>
-    <t>Dundrum</t>
-  </si>
-  <si>
-    <t>Lisburn</t>
-  </si>
-  <si>
-    <t>PSNI</t>
-  </si>
-  <si>
-    <t>Josh Hall</t>
-  </si>
-  <si>
-    <t>Danny Moby</t>
-  </si>
-  <si>
-    <t>Christy Rathesh</t>
-  </si>
-  <si>
-    <t>Joel McKean</t>
-  </si>
-  <si>
-    <t>Erin Smyth</t>
-  </si>
-  <si>
-    <t>Usman Siddiq</t>
-  </si>
-  <si>
-    <t>James Montgomery</t>
-  </si>
-  <si>
-    <t>Indie Allen</t>
-  </si>
-  <si>
-    <t>Vismithaa Pandiaraj</t>
-  </si>
-  <si>
-    <t>Lea Matthews</t>
-  </si>
-  <si>
-    <t>Molly Sawyer</t>
-  </si>
-  <si>
-    <t>Cora Perrin</t>
-  </si>
-  <si>
-    <t>Olivia Boyd</t>
-  </si>
-  <si>
-    <t>Ellie Hipson</t>
-  </si>
-  <si>
-    <t>Sarah Cowden</t>
-  </si>
-  <si>
-    <t>Rachel Murray</t>
-  </si>
-  <si>
-    <t>Lyla Cubitt</t>
-  </si>
-  <si>
-    <t>Ava Templeton</t>
-  </si>
-  <si>
-    <t>Rowan Foye</t>
-  </si>
-  <si>
-    <t>Usman Ahmed</t>
-  </si>
-  <si>
-    <t>Katie Harper</t>
-  </si>
-  <si>
-    <t>Dave Williams</t>
-  </si>
-  <si>
-    <t>Ali Quadri</t>
-  </si>
-  <si>
-    <t>Holywood 1881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NCU Pathway XI </t>
-  </si>
-  <si>
-    <t>Ballymena</t>
-  </si>
-  <si>
-    <t>Templepatrick</t>
-  </si>
-  <si>
-    <t>Bangor</t>
   </si>
 </sst>
 </file>
@@ -229,6 +229,7 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -241,8 +242,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFE0"/>
-        <bgColor rgb="FFFFFFE0"/>
+        <fgColor rgb="FF1F4E78"/>
+        <bgColor rgb="FF1F4E78"/>
       </patternFill>
     </fill>
   </fills>
@@ -544,8 +545,8 @@
   <dimension ref="A1:B43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="31.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -558,338 +559,338 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>57</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>53</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>57</v>
+        <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>12</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="B17" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="B20" t="s">
-        <v>12</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="B21" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="B22" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="B23" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B24" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B25" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="B26" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="B27" t="s">
-        <v>31</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B28" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="B29" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="B30" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="B31" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B32" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="B33" t="s">
-        <v>9</v>
+        <v>53</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B34" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B35" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="B36" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B37" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="B38" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="B39" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="B40" t="s">
-        <v>9</v>
+        <v>53</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B41" t="s">
-        <v>11</v>
+        <v>63</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="B42" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="B43" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
